--- a/artfynd/A 26725-2026 artfynd.xlsx
+++ b/artfynd/A 26725-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127717528</v>
+        <v>17086440</v>
       </c>
       <c r="B2" t="n">
-        <v>98407</v>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillpite, Nb</t>
+          <t>Piteå, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>778760</v>
+        <v>778381</v>
       </c>
       <c r="R2" t="n">
-        <v>7271336</v>
+        <v>7271733</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2006-06-12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>sparsam på platsen, möjlig/säker observation</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -756,64 +761,74 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Äldre granskog i anslutning till  fin opåverkad skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Tomas Lindberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Tomas Lindberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127717557</v>
+        <v>17086441</v>
       </c>
       <c r="B3" t="n">
-        <v>98407</v>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillpite, Nb</t>
+          <t>Piteå, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>778826</v>
+        <v>778969</v>
       </c>
       <c r="R3" t="n">
-        <v>7271253</v>
+        <v>7271170</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +852,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2006-06-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>sparsam på platsen, möjlig/säker observation</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -853,48 +873,58 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Äldre granskog i anslutning till  fin opåverkad skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Tomas Lindberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Tomas Lindberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127717558</v>
+        <v>127717456</v>
       </c>
       <c r="B4" t="n">
-        <v>98407</v>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>778924</v>
+        <v>778848</v>
       </c>
       <c r="R4" t="n">
-        <v>7271161</v>
+        <v>7271263</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127717527</v>
+        <v>127717592</v>
       </c>
       <c r="B5" t="n">
-        <v>98407</v>
+        <v>43378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>201075</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>778453</v>
+        <v>778746</v>
       </c>
       <c r="R5" t="n">
-        <v>7271664</v>
+        <v>7271346</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127717565</v>
+        <v>127717527</v>
       </c>
       <c r="B6" t="n">
-        <v>98407</v>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>778805</v>
+        <v>778453</v>
       </c>
       <c r="R6" t="n">
-        <v>7271288</v>
+        <v>7271664</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1157,6 +1187,496 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127717528</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lillpite, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>778760</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7271336</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127717556</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lillpite, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>778761</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7271305</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Allmänt förekommande längs med vägen</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127717557</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lillpite, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>778826</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7271253</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127717558</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lillpite, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>778924</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7271161</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127717565</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lillpite, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>778805</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7271288</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26725-2026 artfynd.xlsx
+++ b/artfynd/A 26725-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17086441</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17086440</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127717456</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127717592</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127717527</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127717528</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127717556</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127717557</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1580,6 +1625,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127717558</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1677,8 +1727,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127717565</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>